--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -659,8 +659,7 @@
           <t>Integer: switch to estimate or fix numbers-at-age: _x000D_
 0 = estimate dynamics_x000D_
 1 = use input numbers-at-age in NbyageFixed, _x000D_
-2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient_x000D_
-3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
+2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient, estimated under predation (msmMode &gt; 0) and fixed at 1 otherwise.</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1179,7 @@
           <t>Whether selectivity normalization pools its reference across sexes. Orthogonal to 'Sel_norm_bin', which says WHERE the reference is taken (a named bin, or the max). _x000D_
 "WithinSex" = each sex is divided by its own reference, so both reach 1 and only the SHAPE differs by sex (relative sex-specific selectivity removed). _x000D_
 "AcrossSexes" (default) = one reference pooled over both sexes, so the less-selected sex stays below 1 (relative sex-specific selectivity retained). _x000D_
-No effect on a one-sex species, or where 'Sel_norm_bin' is NA (nothing is normalized).</t>
+No effect on a one-sex species, where 'Sel_norm_bin' is "Off" (nothing is normalized), or on a Hake or LogisticPM fleet, which normalize each sex to its own maximum.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -805,6 +805,8 @@
 8 = double normal_x000D_
 9 = non-parametric random walk (AMAK 'pm')_x000D_
 11 = logistic with a free age-1 selectivity (AMAK 'pm')_x000D_
+13 = non-parametric base curve with iid annual deviates carrying a proper density (integrable under random_sel)_x000D_
+14 = non-parametric base curve with random-walk increments carrying a proper density (integrable under random_sel)_x000D_
 Whether a form is age- or length-based is set by Selectivity_dimension, not by the code.</t>
         </is>
       </c>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Number of age or length bins to estimate for non-parametric and AR1 selectivity (Selectivity = 2, 5, 6, 7, or 9).</t>
+          <t>Number of age or length bins to estimate for non-parametric and AR1 selectivity (Selectivity = 2, 5, 6, 7, 9, 13, or 14).</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shape/smoothness penalty weight for non-parametric (type 2/9) and LogisticPM (11) selectivity (the intuitive alternative is Sel_shape_sd). The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across selectivity BINS (ages or length bins, per Selectivity_dimension).</t>
+          <t>Shape/smoothness penalty weight for non-parametric (type 2/9/13/14) and LogisticPM (11) selectivity (the intuitive alternative is Sel_shape_sd). On 13/14 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across selectivity BINS (ages or length bins, per Selectivity_dimension).</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2nd-difference curvature penalty weight for non-parametric (type 2/9) selectivity (the intuitive alternative is Sel_curvature_sd). The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across YEARS.</t>
+          <t>2nd-difference curvature penalty weight for non-parametric (type 2/9/13/14) selectivity (the intuitive alternative is Sel_curvature_sd). On 13/14 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across YEARS.</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
+          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity. Not read by 13/14, whose deviates carry a Gaussian density with Time_varying_sel_sd instead. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9) and LogisticPM (11).</t>
+          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9/13/14) and LogisticPM (11).</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric-only.</t>
+          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric only (2/9/13/14).</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -600,12 +600,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pop_age_transition_index</t>
+          <t>L50_mat_len</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Integer: age transition matrix (e.g. growth trajectory) index to use deriving length-based predation</t>
+          <t>Numeric: length (cm) at which half of females are mature, for maturity-at-length; set with slope_mat_len. NA uses the age-based maturity sheet. Needs estimated growth.</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sigma_rec</t>
+          <t>slope_mat_len</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Numeric: fixed or initial value of standard deviation for recruitment deviates</t>
+          <t>Numeric: slope (per cm, positive) of logistic maturity-at-length, maturity = 1 / (1 + exp(-slope_mat_len * (length - L50_mat_len))). NA uses the age-based maturity sheet.</t>
         </is>
       </c>
     </row>
@@ -634,12 +634,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other_food</t>
+          <t>pop_age_transition_index</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Numeric: other food in the ecosystem for each species (kg)</t>
+          <t>Integer: age transition matrix (e.g. growth trajectory) index to use deriving length-based predation</t>
         </is>
       </c>
     </row>
@@ -651,10 +651,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>sigma_rec</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Numeric: fixed or initial value of standard deviation for recruitment deviates</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other_food</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Numeric: other food in the ecosystem for each species (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>estDynamics</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Integer: switch to estimate or fix numbers-at-age: _x000D_
 0 = estimate dynamics_x000D_
@@ -663,49 +697,15 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Survey and fishery data specifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Fleet_name</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Name of survey or fishery</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Fleet_code</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Index of survey/fishery (does not restart for each species)</t>
+          <t>Survey and fishery data specifications</t>
         </is>
       </c>
     </row>
@@ -717,10 +717,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Fleet_name</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Name of survey or fishery</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fleet_code</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Index of survey/fishery (does not restart for each species)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Fleet_type</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>0 = Do not estimate (fixes all parameters for this fleet to initial values)_x000D_
 1 = Fishery_x000D_
@@ -728,40 +762,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Species number</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Observation month for the fleet (0 = not specified).</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -770,10 +770,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Species number</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Observation month for the fleet (0 = not specified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>Selectivity_index</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Index used to give fleets the SAME selectivity (otherwise, same as Fleet_code). Fleets sharing a value share one selectivity parameter block, with its penalties and priors accumulated once on the group's first non-Off fleet._x000D_
 Sharing the parameters is not enough on its own: the columns that shape the curve are read per fleet and must agree across the group, or the fleets end up with different selectivities. data_check() reports any that differ. To mirror a fleet, copy its fleet_control row and change only the identity and catchability columns._x000D_
@@ -781,18 +815,18 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Selectivity</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>0 = fixed (empirical selectivity from srv_emp_sel)_x000D_
 1 = logistic_x000D_
@@ -807,41 +841,8 @@
 11 = logistic with a free age-1 selectivity (AMAK 'pm')_x000D_
 13 = non-parametric base curve with iid annual deviates carrying a proper density (integrable under random_sel)_x000D_
 14 = non-parametric base curve with random-walk increments carrying a proper density (integrable under random_sel)_x000D_
+15 = Stock Synthesis size pattern 24 double normal (six parameters, varied through selectivity linkages)_x000D_
 Whether a form is age- or length-based is set by Selectivity_dimension, not by the code.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Selectivity_dimension</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>"Age" or "Length".</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>N_sel_bins</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Number of age or length bins to estimate for non-parametric and AR1 selectivity (Selectivity = 2, 5, 6, 7, 9, 13, or 14).</t>
         </is>
       </c>
     </row>
@@ -853,12 +854,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sel_curve_pen1</t>
+          <t>Selectivity_dimension</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shape/smoothness penalty weight for non-parametric (type 2/9/13/14) and LogisticPM (11) selectivity (the intuitive alternative is Sel_shape_sd). On 13/14 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across selectivity BINS (ages or length bins, per Selectivity_dimension).</t>
+          <t>"Age" or "Length".</t>
         </is>
       </c>
     </row>
@@ -870,12 +871,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sel_curve_pen2</t>
+          <t>N_sel_bins</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2nd-difference curvature penalty weight for non-parametric (type 2/9/13/14) selectivity (the intuitive alternative is Sel_curvature_sd). On 13/14 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across YEARS.</t>
+          <t>Number of age or length bins to estimate for non-parametric and AR1 selectivity (Selectivity = 2, 5, 6, 7, 9, 13, or 14).</t>
         </is>
       </c>
     </row>
@@ -887,12 +888,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sel_curve_pen3</t>
+          <t>Sel_curve_pen1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity. Not read by 13/14, whose deviates carry a Gaussian density with Time_varying_sel_sd instead. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
+          <t>Shape/smoothness penalty weight for non-parametric (type 2/9/13/14) and LogisticPM (11) selectivity (the intuitive alternative is Sel_shape_sd). On 13/14 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across selectivity BINS (ages or length bins, per Selectivity_dimension).</t>
         </is>
       </c>
     </row>
@@ -904,10 +905,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Sel_curve_pen2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2nd-difference curvature penalty weight for non-parametric (type 2/9/13/14) selectivity (the intuitive alternative is Sel_curvature_sd). On 13/14 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across YEARS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sel_curve_pen3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity. Not read by 13/14, whose deviates carry a Gaussian density with Time_varying_sel_sd instead. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Time_varying_sel</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Whether to estimate time-varying selectivity for logistic, double logistic, descending logistic, or non-parametric forms._x000D_
 0 or "Off" = no_x000D_
@@ -920,40 +955,6 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Time_varying_sel_sd</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Sel_start_year</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>First year the fleet's time-varying selectivity deviations are estimated and penalized (NA -&gt; earliest year of data across fleets sharing the Selectivity_index, bounded below by styr).</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -962,50 +963,50 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Time_varying_sel_sd</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sel_start_year</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>First year the fleet's time-varying selectivity deviations are estimated and penalized (NA -&gt; earliest year of data across fleets sharing the Selectivity_index, bounded below by styr).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>Bin_first_selected</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>First age/length bin selected; selectivity is 0 below it. _x000D_
 A 1-based BIN ORDINAL on the fleet's 'Selectivity_dimension' -- 3 means the third bin, so on a stock with 'minage' 3 it is age 5, not age 3. This is the opposite convention to 'Sel_norm_bin', which is an absolute age. The alias 'Age_first_selected' is the older name for the same column, not a second convention.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Sel_shape_sd</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9/13/14) and LogisticPM (11).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sel_curvature_sd</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric only (2/9/13/14).</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -1014,12 +1015,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sel_devmag_sd</t>
+          <t>Sel_shape_sd</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Deviation-magnitude selectivity penalty expressed as a standard deviation (Sel_curve_pen3). NonParametric (2/9) and LogisticPM (11).</t>
+          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9/13/14) and LogisticPM (11).</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1032,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sel_shape_dir</t>
+          <t>Sel_curvature_sd</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Direction of the (directional-mode) NonParametric shape penalty when Sel_shape_sd is used: "Decreasing" (default) or "Increasing".</t>
+          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric only (2/9/13/14).</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1049,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sel_pen_first_bin</t>
+          <t>Sel_devmag_sd</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>First bin (age or length) for the non-parametric shape penalty (NA -&gt; Bin_first_selected).</t>
+          <t>Deviation-magnitude selectivity penalty expressed as a standard deviation (Sel_curve_pen3). NonParametric (2/9) and LogisticPM (11).</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1066,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sel_pen_last_bin</t>
+          <t>Sel_shape_dir</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Last (left) bin of the shape-penalty pairs (NA -&gt; nbins-2).</t>
+          <t>Direction of the (directional-mode) NonParametric shape penalty when Sel_shape_sd is used: "Decreasing" (default) or "Increasing".</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1083,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sel_shape_mode</t>
+          <t>Sel_pen_first_bin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shape-penalty mode: "Directional" (default) or "Smooth" (two-sided d^2, RTMB).</t>
+          <t>First bin (age or length) for the non-parametric shape penalty (NA -&gt; Bin_first_selected).</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1100,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sel_avgsel_pen</t>
+          <t>Sel_pen_last_bin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Weight on the AMAK avgsel base-level penalty (type 9); 0 = off (default), 10 matches AMAK.</t>
+          <t>Last (left) bin of the shape-penalty pairs (NA -&gt; nbins-2).</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1117,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sel_cap_bin</t>
+          <t>Sel_shape_mode</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NonParametricRPM bin cap (NA -&gt; no cap).</t>
+          <t>Shape-penalty mode: "Directional" (default) or "Smooth" (two-sided d^2, RTMB).</t>
         </is>
       </c>
     </row>
@@ -1133,10 +1134,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>Sel_avgsel_pen</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Weight on the AMAK avgsel base-level penalty (type 9); 0 = off (default), 10 matches AMAK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sel_cap_bin</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NonParametricRPM bin cap (NA -&gt; no cap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Sel_norm_bin</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Where selectivity is normalized to 1. Takes a word or a bin:_x000D_
 "Max" = normalize by the largest value._x000D_
@@ -1148,35 +1183,35 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Sel_norm_bin_upper</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Upper age/length bin for selectivity normalization. "Off" (or blank) uses a single bin rather than a range; a number takes mean selectivity between 'Sel_norm_bin' and this bin, on the same scale and with the same bounds as 'Sel_norm_bin'.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Sel_norm_scope</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Whether selectivity normalization pools its reference across sexes. Orthogonal to 'Sel_norm_bin', which says WHERE the reference is taken (a named bin, or the max). _x000D_
 "WithinSex" = each sex is divided by its own reference, so both reach 1 and only the SHAPE differs by sex (relative sex-specific selectivity removed). _x000D_
@@ -1185,18 +1220,18 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>Comp_distribution</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 -1 = AFSC multinomial_x000D_
@@ -1205,18 +1240,18 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Comp_weights</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Composition weight, on a scale set by 'Comp_distribution'. _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
@@ -1226,18 +1261,18 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>CAAL_distribution</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 -1 = AFSC multinomial_x000D_
@@ -1246,40 +1281,6 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>CAAL_weights</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Conditional age-at-length composition weight, on a scale set by 'CAAL_distribution', exactly as 'Comp_weights' is. Under a Dirichlet-multinomial the column is the LOG of the starting weight, so the default of 1 is a starting weight of e.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Comp_accum_young</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Age/length composition young-tail accumulation bin (AFSC ac_yng): a 1-based ordinal on the fleet's composition dimension; bins below it are folded into it before the likelihood. NA or 1 = no young accumulation.</t>
-        </is>
-      </c>
-    </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
@@ -1288,12 +1289,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Comp_accum_old</t>
+          <t>CAAL_weights</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Age/length composition old-tail accumulation bin (AFSC ac_old): a 1-based ordinal on the fleet's composition dimension; bins above it are folded into it before the likelihood. NA, 0, or a value &gt;= the number of bins = no old accumulation.</t>
+          <t>Conditional age-at-length composition weight, on a scale set by 'CAAL_distribution', exactly as 'Comp_weights' is. Under a Dirichlet-multinomial the column is the LOG of the starting weight, so the default of 1 is a starting weight of e.</t>
         </is>
       </c>
     </row>
@@ -1305,10 +1306,44 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>Comp_accum_young</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Age/length composition young-tail accumulation bin (AFSC ac_yng): a 1-based ordinal on the fleet's composition dimension; bins below it are folded into it before the likelihood. NA or 1 = no young accumulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Comp_accum_old</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Age/length composition old-tail accumulation bin (AFSC ac_old): a 1-based ordinal on the fleet's composition dimension; bins above it are folded into it before the likelihood. NA, 0, or a value &gt;= the number of bins = no old accumulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>Observation_units</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>1 = catch/index is weight (mt) _x000D_
 2 = catch/index is in numbers (thousands of fish) _x000D_
@@ -1316,40 +1351,6 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Weight_index</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Weight index to use for calculation of derived quantities</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Age_transition_index</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
-        </is>
-      </c>
-    </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
@@ -1358,10 +1359,44 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>Weight_index</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Weight index to use for calculation of derived quantities</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Age_transition_index</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Catchability_index</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Index used to give fleets the SAME catchability (otherwise, same as Fleet_code). Fleets sharing a value share one q parameter, so the group carries only one answer to whether q is estimated: the group's first non-Off fleet decides for all of them, regardless of fleet type. Give a fleet its own value when it should be estimated independently._x000D_
 'Analytical' and 'AnalyticalArith' are the exception -- they solve q from each fleet's own index observations, so a group containing one does NOT share a catchability. data_check() reports that case, a Fixed lead that leaves fleets on different inits, and a Catchability or Time_varying_q that differs within a group._x000D_
@@ -1369,18 +1404,18 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>Catchability</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Catchability form. Accepts integer codes or readable strings:_x000D_
 0 or "Fixed" = fixed at Catchability_init_x000D_
@@ -1395,40 +1430,6 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Catchability_init</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Starting value or fixed value for catchability. Must be positive on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and it is logged to seed index_log_q, so a blank or zero gives a non-finite starting value. Not read under Analytical or AnalyticalArith, which solve q from the data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Catchability_prior_sd</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Standard deviation for the q prior, on the log scale. Must be positive under Estimated-with-prior, where the prior is scored at it.</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
@@ -1437,10 +1438,44 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>Catchability_init</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Starting value or fixed value for catchability. Must be positive on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and it is logged to seed index_log_q, so a blank or zero gives a non-finite starting value. Not read under Analytical or AnalyticalArith, which solve q from the data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Catchability_prior_sd</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Standard deviation for the q prior, on the log scale. Must be positive under Estimated-with-prior, where the prior is scored at it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>Time_varying_q</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>0 or "Off" = no_x000D_
 1 or "IID" = penalized deviate or random effect_x000D_
@@ -1453,35 +1488,35 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Time_varying_q_sd</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Starting or fixed sd for the time-varying q deviations. Must be positive when Time_varying_q is IID, AR1 or RandomWalk, which penalize the deviations at it; Block needs none.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>Index_distribution</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Survey/index biomass observation likelihood family._x000D_
 0 or "Lognormal" (default) = independent lognormal on the log observation, with the bias correction._x000D_
@@ -1491,18 +1526,18 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Estimate_index_sd</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from index_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1510,35 +1545,35 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>Index_sd</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Starting value to be used if "Estimate_index_sd" = 1</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>Estimate_catch_sd</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from catch_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1546,186 +1581,186 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Catch_sd</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Starting value to be used if Estimate_catch_sd = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Proj_F_proportion</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>The proportion of future fishing mortality assigned to this fleet</t>
-        </is>
-      </c>
-    </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>index_data</t>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Catch_sd</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Survey index or fishery indices in weight (mt) or numbers (thousands of fish).</t>
+          <t>Starting value to be used if Estimate_catch_sd = 1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>catch_data</t>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Proj_F_proportion</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Total catch in weight (mt) or numbers data</t>
+          <t>The proportion of future fishing mortality assigned to this fleet</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comp_data</t>
+          <t>index_data</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
+          <t>Survey index or fishery indices in weight (mt) or numbers (thousands of fish).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>caal_data</t>
+          <t>catch_data</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
+          <t>Total catch in weight (mt) or numbers data</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>emp_sel</t>
+          <t>comp_data</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
+          <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>caal_data</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>emp_sel</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>age_trans_matrix</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. _x000D_
 Can have multiple matrices for a species specified by Age_transition_index.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>age_error</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Aging error matrices. Can have only one per species.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Time-invariant or -varying empirical weight-at-age for calculation of derived quantities (SSB, Consumption/Ration, Suitability, Total Catch, Survey Biomass, etc). _x000D_
 Can have multiple weight-at-age data-sets for each species.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>maturity</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Maturity-at-age for each species</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>sex_ratio</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Percent female at age for each species</t>
-        </is>
-      </c>
-    </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>M1_base</t>
+          <t>maturity</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Residual natural mortality for each species</t>
+          <t>Maturity-at-age for each species</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>sex_ratio</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Percent female at age for each species</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>M1_base</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Residual natural mortality for each species</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Ceq</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumption: _x000D_
 1 = Exponential (Stewart et al 1983)_x000D_
@@ -1735,40 +1770,6 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Cindex</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Integer: which environmental index in env_data drives bioenergetics, counting the covariate columns from 1 (the Year column is not one). Read only when Ceq is 1, 2 or 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Pvalue</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
-        </is>
-      </c>
-    </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
@@ -1777,12 +1778,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>fday</t>
+          <t>Cindex</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Numeric: number of foraging days per year for each species</t>
+          <t>Integer: which environmental index in env_data drives bioenergetics, counting the covariate columns from 1 (the Year column is not one). Read only when Ceq is 1, 2 or 3.</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1795,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Pvalue</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1812,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>fday</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+          <t>Numeric: number of foraging days per year for each species</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1829,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Qc</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1846,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tco</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1863,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tcm</t>
+          <t>Qc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1879,7 +1880,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tcl</t>
+          <t>Tco</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1896,7 +1897,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CK1</t>
+          <t>Tcm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1913,7 +1914,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CK4</t>
+          <t>Tcl</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -1930,10 +1931,44 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>CK1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CK4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>Diet_distribution</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Diet composition likelihood distribution per predator species:_x000D_
 0 = multinomial_x000D_
@@ -1941,18 +1976,18 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Diet_comp_weights</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Diet composition weight per predator species, on a scale set by 'Diet_distribution' (as for 'Comp_weights'). _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
@@ -1961,37 +1996,37 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>env_data</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specified by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in Celsius.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>ration_data</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
-        </is>
-      </c>
-    </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>env_data</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specified by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in Celsius.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ration_data</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>diet_data</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Multiple diet-data formats can be included:_x000D_
 _x000D_
@@ -2006,36 +2041,36 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>NOTE: Most objects are ordered by species code if not specified</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>NOTE: Lengths are index 1 through nlengths</t>
-        </is>
-      </c>
-    </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NOTE: Columns for ages are index by 1 through nages, but are placeholders.</t>
+          <t>NOTE: Most objects are ordered by species code if not specified</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
+          <t>NOTE: Lengths are index 1 through nlengths</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
+        <is>
+          <t>NOTE: Columns for ages are index by 1 through nages, but are placeholders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>NOTE: For emp_sel, weight, and ration_data, if "Year" == 0, those data will be used for all years</t>
         </is>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -803,10 +803,9 @@
 6 = 2D AR1 (age x year)_x000D_
 7 = 3D AR1 (Cheng et al. 2024)_x000D_
 8 = double normal_x000D_
-9 = non-parametric random walk (AMAK 'pm')_x000D_
+9 = non-parametric random walk, increments penalized (AMAK 'pm'; not integrable under random_sel)_x000D_
 11 = logistic with a free age-1 selectivity (AMAK 'pm')_x000D_
-13 = non-parametric base curve with iid annual deviates carrying a proper density (integrable under random_sel)_x000D_
-14 = non-parametric base curve with random-walk increments carrying a proper density (integrable under random_sel)_x000D_
+13 = non-parametric base curve whose deviations have a proper density, so random_sel integrates them; Time_varying_sel picks the structure (Off, IID or RandomWalk)_x000D_
 Whether a form is age- or length-based is set by Selectivity_dimension, not by the code.</t>
         </is>
       </c>
@@ -1121,7 +1120,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NonParametricRPM bin cap (NA -&gt; no cap).</t>
+          <t>NonParametricPM bin cap (NA -&gt; no cap).</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Number of age or length bins to estimate for non-parametric and AR1 selectivity (Selectivity = 2, 5, 6, 7, 9, 13, or 14).</t>
+          <t>Number of age or length bins to estimate for non-parametric and AR1 selectivity (Selectivity = 2, 5, 6, 7, 9, or 13).</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shape/smoothness penalty weight for non-parametric (type 2/9/13/14) and LogisticPM (11) selectivity (the intuitive alternative is Sel_shape_sd). On 13/14 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across selectivity BINS (ages or length bins, per Selectivity_dimension).</t>
+          <t>Shape/smoothness penalty weight for non-parametric (type 2/9/13) and LogisticPM (11) selectivity (the intuitive alternative is Sel_shape_sd). On 13 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across selectivity BINS (ages or length bins, per Selectivity_dimension).</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2nd-difference curvature penalty weight for non-parametric (type 2/9/13/14) selectivity (the intuitive alternative is Sel_curvature_sd). On 13/14 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across YEARS.</t>
+          <t>2nd-difference curvature penalty weight for non-parametric (type 2/9/13) selectivity (the intuitive alternative is Sel_curvature_sd). On 13 it is charged once on the base coefficients, not on each year's curve. The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across YEARS.</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity. Not read by 13/14, whose deviates carry a Gaussian density with Time_varying_sel_sd instead. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
+          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity. Not read by 13, whose deviates carry a Gaussian density with Time_varying_sel_sd instead. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9/13/14) and LogisticPM (11).</t>
+          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9/13) and LogisticPM (11).</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric only (2/9/13/14).</t>
+          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric only (2/9/13).</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity. Not read by 13, whose deviates carry a Gaussian density with Time_varying_sel_sd instead. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
+          <t>Deviation-magnitude penalty weight (Sel_curve_pen3). Read only by "NonParametricPM" (9) and "LogisticPM" (11): "NonParametric" (2) has no deviate term and "NonParametricIntegrable" (13) scores its deviates with Time_varying_sel_sd instead. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Deviation-magnitude selectivity penalty expressed as a standard deviation (Sel_curve_pen3). NonParametric (2/9) and LogisticPM (11).</t>
+          <t>Deviation-magnitude selectivity penalty expressed as a standard deviation (Sel_curve_pen3). "NonParametricPM" (9) and "LogisticPM" (11) only; the slot is not read by "NonParametric" (2) or "NonParametricIntegrable" (13).</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Direction of the (directional-mode) NonParametric shape penalty when Sel_shape_sd is used: "Decreasing" (default) or "Increasing".</t>
+          <t>Direction of the shape penalty when Sel_shape_sd is used: "Decreasing" (default) or "Increasing". Only "NonParametricPM" (9) with Sel_shape_mode = "Directional" branches on the direction; every other form, that one under "Smooth" included, applies the weight as written, so "Increasing" is refused there rather than negating it.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deviation-magnitude penalty weight (Sel_curve_pen3). Read only by "NonParametricPM" (9) and "LogisticPM" (11): "NonParametric" (2) has no deviate term and "NonParametricIntegrable" (13) scores its deviates with Time_varying_sel_sd instead. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
+          <t>Deviation-magnitude penalty weight (Sel_curve_pen3). Read only by "NonParametricPM" (9) and "LogisticPM" (11). "NonParametric" (2) and "NonParametricIntegrable" (13) do have selectivity deviates, but score them with a Gaussian density on Time_varying_sel_sd instead, so this slot is inert on both. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Numeric: other food in the ecosystem for each species (kg)</t>
+          <t>Numeric: other food in the ecosystem for each species (mt)</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specified by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in Celsius.</t>
+          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specified by Ceq and Cindex. Also used to drive catchability if Catchability = 5. Will use the mean for missing years. Temperature should be in Celsius.</t>
         </is>
       </c>
     </row>
